--- a/public/templates/student-upload-template.xlsx
+++ b/public/templates/student-upload-template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -497,77 +497,868 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Akello Sharon</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Primary 1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Mr. Okello</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>+256701234567</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Amina Nakato</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baby Class</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sarah Nakato</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+256771234567</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Mukasa David</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Primary 1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Brian Okello</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Baby Class</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Peter Okello</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+256772345678</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Catherine Nampiima</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Middle Class</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Grace Nampiima</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+256773456789</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Daniel Wasswa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Middle Class</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Robert Wasswa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+256774567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esther Kyomuhangi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Top Class</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Joy Kyomuhangi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+256775678901</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Francis Ssekitoleko</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Top Class</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>David Ssekitoleko</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+256776789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Grace Mbabazi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Primary One</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Martha Mbabazi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+256777890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Henry Kato</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Primary One</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Mrs. Mukasa</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>+256782255758</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Nambi Grace</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Primary 2</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mr. Nambi</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Joseph Kato</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+256778901234</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Irene Nansubuga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Primary Two</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rebecca Nansubuga</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+256779012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>James Ssali</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primary Two</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>John Ssali</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+256780123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kevin Mukasa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Primary Three</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sarah Mukasa</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+256781234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lillian Nakamya</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Primary Three</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Grace Nakamya</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+256782345678</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Micheal Okwir</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primary Four</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Peter Okwir</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+256783456789</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nancy Achieng</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Primary Four</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mary Achieng</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+256784567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oscar Odongo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Primary Five</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sam Odongo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+256785678901</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Patience Nakiwala</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Primary Five</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Faith Nakiwala</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+256786789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Quinn Sempijja</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Primary Six</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Paul Sempijja</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+256787890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rita Nansubuga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Primary Six</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Martha Nansubuga</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+256788901234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samuel Wasswa</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primary Seven</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Peter Wasswa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+256789012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tracy Namugga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Primary Seven</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Esther Namugga</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+256790123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Andrew Ssentongo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Senior One</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Henry Ssentongo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>+256791234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brenda Nakitende</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Senior One</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sarah Nakitende</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>+256792345678</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Charles Muwonge</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Senior Two</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>John Muwonge</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>+256793456789</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Diana Nalwoga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Senior Two</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Grace Nalwoga</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>+256794567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Edward Ssempijja</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Senior Three</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Robert Ssempijja</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+256795678901</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fiona Nakato</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Senior Three</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Joy Nakato</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+256796789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>George Lukwago</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Senior Four</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>David Lukwago</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+256797890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Helen Nakanwagi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Senior Four</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sarah Nakanwagi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>+256798901234</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Isaac Kiggundu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Senior Five</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Paul Kiggundu</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+256799012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jackie Namuyomba</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Senior Five</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mary Namuyomba</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>+256700123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kenneth Ssembatya</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Senior Six</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>John Ssembatya</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+256701234568</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lydia Nakato</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Senior Six</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Grace Nakato</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>+256702345679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
